--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_649_Russia_Far_East.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_649_Russia_Far_East.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra57c684df18e4b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R577f81ba61f34c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfdb5c82a22764703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc53bd5d58a34426f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb7d7e588b3544b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0ba07638a5484a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd0cb845f6f134324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R81418c0534614ccd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R9a1408dad7a8468a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd81439fee61c4422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7d7201ce66d24f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R943f82c89b7c47d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ649CommercialTable" displayName="EEZ649CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ649CommercialTable" displayName="EEZ649CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ649FunctionalTable" displayName="EEZ649FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ649FunctionalTable" displayName="EEZ649FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ649ValidationTable" displayName="EEZ649ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ649ValidationTable" displayName="EEZ649ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6456,7 +6410,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda17ade612254709"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3293d4370d2442c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6466,20 +6420,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6487,714 +6431,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>16248.9851034891</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.140005538807466</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>138.04018695500915</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>16248.9851034891</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>138.04031435291586</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$87,A2,'Species'!$U$2:$U$87))</x:f>
-        <x:v>2243015.0116014825</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.140005538807466</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>138.04018695500915</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2243012.941514794</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2.070086688734591</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000009229044784</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>9.229044783560549e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3951035.9564855844</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6133336785775465</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>410.51939347128547</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3951035.9564855844</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>448.63568867352274</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1772575737.3117607</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6133336785775465</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>410.51939347128547</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1621976884.4397023</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>150598852.8720584</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0928489513733615</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.09284895137336155</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>217859.4006237841</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.927566740531207</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>84.63826273005418</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>217859.4006237841</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>184.69626163892957</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$87,A4,'Species'!$U$2:$U$87))</x:f>
-        <x:v>40237816.85811081</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.927566740531207</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>84.63826273005418</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>18439241.18820797</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>21798575.66990284</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.1821839872588242</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.1821839872588245</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>145887.8243317146</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6745765926660807</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>472.6901937249197</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>145887.8243317146</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>617.3212168345091</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>90059649.23779315</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6745765926660807</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>472.6901937249197</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>68959743.94546522</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>21099905.292327926</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3059742406963426</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.30597424069634255</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>830407.9527512426</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1074788537232783</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>128.07927298091133</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>830407.9527512426</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>132.17510269611208</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>109759256.43456368</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1074788537232783</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>128.07927298091133</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>106358046.86594611</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3401209.5686175674</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0319788644944228</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.031978864494422866</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>25441.5271622189</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.483272867762853</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>30.427962178573875</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>25441.5271622189</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>53.55492898012478</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1362519.1803185486</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.483272867762853</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>30.427962178573875</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>774133.8262571566</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>588385.354061392</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7600563805694476</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7600563805694476</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>944089.2446144465</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.411212332633833</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>257.7581064343074</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>944089.2446144465</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>399.7565016695926</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>377405813.6909594</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.411212332633833</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>257.7581064343074</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>243346655.9968154</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>134059157.69414398</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5508978832891722</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5508978832891723</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>160445.94627571598</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.324520345576297</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>211.1156095709681</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>160445.94627571598</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>333.0607499816792</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>53438247.19811017</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.324520345576297</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>211.1156095709681</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>33872643.751188576</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>19565603.446921594</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.577622567362639</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.577622567362639</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>991945.106119383</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.139210702137463</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1377.8777973999581</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>991945.106119383</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1959.300652375116</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1943518693.5400107</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.139210702137463</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1377.8777973999581</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1366779137.9614432</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>576739555.5785675</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4219698264042697</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.42196982640426967</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>40404.529895944404</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3994488384489263</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>250.87006275278748</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>40404.529895944404</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>254.33992605223403</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$87,A11,'Species'!$U$2:$U$87))</x:f>
-        <x:v>10276485.145909779</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3994488384489263</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>250.87006275278748</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>10136286.950492451</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>140198.1954173278</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0138313167437034</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01383131674370333</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>17729.4608366277</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.7200094495649907</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>524.8188793590693</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>17729.4608366277</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>524.8250258831791</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$87,A12,'Species'!$U$2:$U$87))</x:f>
-        <x:v>9304864.742477942</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.7200094495649907</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>524.8188793590693</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9304755.767919457</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>108.97455848567188</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0000117117054121</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.000011711705412128038</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>480.92830766279997</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.321824963092508</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2098.094102856903</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>480.92830766279997</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2112.1558510605646</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$87,A13,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1015795.5389706383</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.321824963092508</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2098.094102856903</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1009032.846204271</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>6762.692766367341</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.006702153246851</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.00670215324685108</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa16f14a9798441a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4c582474afe4d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,20 +6684,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7225,1146 +6695,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>174237.78048632172</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.102304993087613</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1265.6248490231346</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>174237.78048632172</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1310.4128590436756</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$87,A2,'Species'!$U$2:$U$87))</x:f>
-        <x:v>228323428.0805052</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.102304993087613</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1265.6248490231346</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>220519664.622127</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7803763.458378196</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0353880615216353</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.03538806152163522</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>447.8</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4599999999999995</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.4031503126603</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>447.8</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$87,A3,'Species'!$U$2:$U$87))</x:f>
-        <x:v>129146.9307100094</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4599999999999995</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.4031503126603</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>129146.93071000927</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1.3096723705530167e-10</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.0140948479014168e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>432.8</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>432.8</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$87,A4,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>299424.4442137156</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>299424.4442137156</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>298989.9259657335</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7576479194700045</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>572.3318560675366</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>298989.9259657335</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>643.4369145973158</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$87,A5,'Species'!$U$2:$U$87))</x:f>
-        <x:v>192381155.45907143</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7576479194700045</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>572.3318560675366</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>171121459.2734636</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>21259696.18560782</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1242374642892297</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.12423746428922977</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>270058.07949170953</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.171388586644858</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1483.8451674770647</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>270058.07949170953</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1486.538221647255</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$87,A6,'Species'!$U$2:$U$87))</x:f>
-        <x:v>401451657.22907895</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.171388586644858</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1483.8451674770647</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>400724376.1919102</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>727281.0371687412</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0018149158882723</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0018149158882723928</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7806.987143770901</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.171624359574801</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1484.6509467793064</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7806.987143770901</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1501.9162930993036</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$87,A7,'Species'!$U$2:$U$87))</x:f>
-        <x:v>11725441.191246312</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.171624359574801</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1484.6509467793064</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>11590650.85449334</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>134790.33675297163</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0116292293198288</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.011629229319828708</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>480.92830766279997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.321824963092508</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2098.094102856903</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>480.92830766279997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2112.1558510605646</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$87,A8,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1015795.5389706383</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.321824963092508</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2098.094102856903</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1009032.846204271</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>6762.692766367341</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.006702153246851</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00670215324685108</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>17728.9661997478</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.7199999999999998</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>524.8074602497722</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>17728.9661997478</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$87,A9,'Species'!$U$2:$U$87))</x:f>
-        <x:v>9304293.72414371</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.7199999999999998</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>524.8074602497722</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9304293.724143699</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.1175870895385742e-8</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.20115198710736e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.4946368799</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.058704409709341</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1144.733545635926</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.4946368799</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1154.4192465932167</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$87,A10,'Species'!$U$2:$U$87))</x:f>
-        <x:v>571.0183342313774</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.058704409709341</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1144.733545635926</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>566.2274293302187</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4.790904901158683</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0084610964658243</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008461096465824285</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>153542.318734144</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.988178041678346</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>97.31460892022807</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>153542.318734144</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>233.4782994332307</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$87,A11,'Species'!$U$2:$U$87))</x:f>
-        <x:v>35848799.46908302</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.988178041678346</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>97.31460892022807</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>14941910.700318232</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>20906888.768764786</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>2.3992111978235497</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>1.3992111978235495</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>977.9226753647999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5822383232025734</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>382.15392388868815</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>977.9226753647999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>391.22175266110037</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$87,A12,'Species'!$U$2:$U$87))</x:f>
-        <x:v>382584.6230232493</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5822383232025734</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>382.15392388868815</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>373716.98765038204</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8867.635372867284</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.023728210560134</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.023728210560134057</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3657420.9327724264</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5706388458729705</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>372.08215846566213</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3657420.9327724264</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>372.3232527801656</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$87,A13,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1361742858.476097</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5706388458729705</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>372.08215846566213</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1360861075.0834599</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>881783.3926372528</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0006479598900888</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0006479598900888352</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>1370699.8805229478</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.7994387441014514</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>630.142460070023</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>1370699.8805229478</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1379.1359870031067</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$87,A14,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1890381532.610056</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.7994387441014514</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>630.142460070023</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>863736194.730417</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1026645337.8796389</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.1886098372895764</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.1886098372895766</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1031087.6488724136</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.1791935724743485</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>151.0753372723306</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1031087.6488724136</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>167.76910428528276</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$87,A15,'Species'!$U$2:$U$87))</x:f>
-        <x:v>172984651.29094297</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.1791935724743485</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>151.0753372723306</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>155771914.31073424</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>17212736.980208725</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1104996177030522</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1104996177030521</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>7828.2485361559</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>4.010102511482339</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>1023.534560311523</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>7828.2485361559</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1040.397962704333</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$87,A16,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8144493.828559776</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>4.010102511482339</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>1023.534560311523</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>8012482.923463653</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>132010.905096123</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0164756550943208</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.01647565509432088</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>53583.3231801479</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.386100293819392</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>24.327657550975818</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>53583.3231801479</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>37.30633039669418</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$87,A17,'Species'!$U$2:$U$87))</x:f>
-        <x:v>1998997.1583114392</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.386100293819392</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>24.327657550975818</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1303556.7367699025</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>695440.4215415367</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.533494555261765</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5334945552617649</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>64317.0818896401</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.7828711255219023</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>60.65563106599213</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>64317.0818896401</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>68.24030661961291</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$87,A18,'Species'!$U$2:$U$87))</x:f>
-        <x:v>4389017.389027793</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.7828711255219023</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>60.65563106599213</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>3901193.190339214</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>487824.1986885788</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1250448708606922</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.1250448708606922</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>41805.7616890079</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>41805.7616890079</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$87,A19,'Species'!$U$2:$U$87))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>4180576.16890079</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>4180576.16890079</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>52449.1442157961</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1799542471982294</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>151.3401803582395</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>52449.1442157961</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>155.94651421024392</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$87,A20,'Species'!$U$2:$U$87))</x:f>
-        <x:v>8179261.213763779</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1799542471982294</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>151.3401803582395</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7937662.9452538965</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>241598.2685098825</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0304369523090344</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.030436952309034416</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>138080.83718794372</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.646473884099687</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>443.0715699857315</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>138080.83718794372</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>567.3068735810537</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$87,A21,'Species'!$U$2:$U$87))</x:f>
-        <x:v>78334208.04654683</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.646473884099687</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>443.0715699857315</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>61179693.3178064</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>17154514.72874043</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2803955658886508</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.2803955658886508</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dd0e22b21ea454c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d1ece0ddf64a9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8539,7 +7265,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8638,7 +7364,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4411197893.890587</x:v>
+        <x:v>3483199576.481157</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8652,7 +7378,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4411197893.890587</x:v>
+        <x:v>3296898592.209809</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8666,7 +7392,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-927998317.40943</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8680,7 +7406,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1114299301.680778</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8691,9 +7417,9 @@
         <x:v>EEZ_649</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8705,47 +7431,19 @@
         <x:v>EEZ_649</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_649</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_649</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24ea7e9e4458462c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e159b94ab894b38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8792,7 +7490,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
